--- a/data/trans_bre/P2A_lim_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_lim_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,18</t>
+          <t>0,06; 4,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,7</t>
+          <t>-1,58; 4,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 1,07</t>
+          <t>-3,85; 0,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 8,52</t>
+          <t>-2,61; 8,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 369,18</t>
+          <t>-2,34; 360,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 165,73</t>
+          <t>-30,35; 142,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-72,03; 46,01</t>
+          <t>-71,67; 37,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-29,2; 287,69</t>
+          <t>-36,41; 280,56</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,85</t>
+          <t>-2,12; 1,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 2,89</t>
+          <t>-2,76; 2,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,83</t>
+          <t>-2,17; 2,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,6; -0,91</t>
+          <t>-10,41; -0,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,62; 76,75</t>
+          <t>-51,74; 67,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,58; 60,96</t>
+          <t>-38,5; 55,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,15; 67,59</t>
+          <t>-46,96; 80,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,2; -11,61</t>
+          <t>-70,65; -9,18</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,74</t>
+          <t>-1,5; 3,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 5,53</t>
+          <t>-0,89; 5,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,1</t>
+          <t>-1,41; 3,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 4,84</t>
+          <t>-1,17; 4,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 96,31</t>
+          <t>-23,74; 100,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 98,4</t>
+          <t>-11,73; 91,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 90,83</t>
+          <t>-25,04; 96,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 110,63</t>
+          <t>-17,11; 105,27</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 7,4</t>
+          <t>0,33; 7,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 6,86</t>
+          <t>-0,81; 6,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 1,34</t>
+          <t>-5,0; 1,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 8,66</t>
+          <t>-3,57; 9,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 138,42</t>
+          <t>2,8; 132,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 94,32</t>
+          <t>-7,41; 89,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,32; 17,15</t>
+          <t>-42,76; 20,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 187,99</t>
+          <t>-24,17; 174,99</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 2,07</t>
+          <t>-6,63; 2,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 6,28</t>
+          <t>-3,74; 5,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 8,6</t>
+          <t>-0,14; 8,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -2,51</t>
+          <t>-9,85; -2,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,54; 23,43</t>
+          <t>-45,09; 25,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 57,24</t>
+          <t>-23,91; 54,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 98,62</t>
+          <t>-1,64; 107,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-47,94; -13,72</t>
+          <t>-47,35; -14,27</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 3,92</t>
+          <t>-5,45; 3,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 3,65</t>
+          <t>-7,86; 3,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 7,08</t>
+          <t>-1,99; 7,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 61,0</t>
+          <t>-0,57; 61,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,48; 42,69</t>
+          <t>-38,31; 41,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,57; 28,42</t>
+          <t>-40,98; 30,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 92,43</t>
+          <t>-16,81; 100,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 446,78</t>
+          <t>-3,79; 416,86</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 7,57</t>
+          <t>-4,8; 7,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 8,87</t>
+          <t>-4,98; 9,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 14,01</t>
+          <t>3,42; 14,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 12,57</t>
+          <t>1,83; 12,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 61,34</t>
+          <t>-25,32; 65,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,72; 56,43</t>
+          <t>-20,27; 55,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,18; 218,68</t>
+          <t>28,56; 223,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,22; 48,8</t>
+          <t>5,62; 50,84</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,69</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,55</t>
+          <t>0,59; 3,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,92</t>
+          <t>0,35; 3,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 20,58</t>
+          <t>0,26; 21,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 44,83</t>
+          <t>-0,0; 44,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,5; 41,62</t>
+          <t>5,91; 40,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,3; 46,53</t>
+          <t>4,5; 47,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,86; 191,86</t>
+          <t>1,94; 181,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_lim_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_lim_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,27</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>56,0%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 4,32</t>
+          <t>-0,03; 4,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 4,29</t>
+          <t>-1,34; 4,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,86</t>
+          <t>-3,72; 1,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 8,66</t>
+          <t>-1,59; 9,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 360,89</t>
+          <t>-10,1; 365,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,35; 142,56</t>
+          <t>-27,57; 152,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-71,67; 37,51</t>
+          <t>-71,14; 50,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 280,56</t>
+          <t>-26,22; 250,38</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,45</t>
+          <t>-3,89</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-47,36%</t>
+          <t>-36,08%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,63</t>
+          <t>-2,1; 1,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,67</t>
+          <t>-2,71; 2,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,09</t>
+          <t>-2,26; 2,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,41; -0,62</t>
+          <t>-8,33; 0,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,74; 67,38</t>
+          <t>-48,29; 72,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,5; 55,6</t>
+          <t>-37,03; 54,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,96; 80,13</t>
+          <t>-47,51; 90,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,65; -9,18</t>
+          <t>-61,76; 3,41</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>50,25%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,72</t>
+          <t>-1,53; 3,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 5,3</t>
+          <t>-1,0; 5,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 3,25</t>
+          <t>-1,61; 3,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,83</t>
+          <t>0,04; 5,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,74; 100,46</t>
+          <t>-26,44; 97,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 91,16</t>
+          <t>-11,15; 93,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 96,74</t>
+          <t>-29,63; 91,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 105,27</t>
+          <t>-1,84; 128,47</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>-1,56</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>-11,05%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 7,44</t>
+          <t>0,34; 7,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 6,74</t>
+          <t>-0,65; 7,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 1,61</t>
+          <t>-4,72; 1,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 9,25</t>
+          <t>-4,94; 1,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 132,44</t>
+          <t>0,77; 142,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 89,77</t>
+          <t>-6,21; 89,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 20,96</t>
+          <t>-41,84; 20,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 174,99</t>
+          <t>-30,85; 15,33</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-6,21</t>
+          <t>-5,18</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-33,06%</t>
+          <t>-28,34%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 2,36</t>
+          <t>-6,64; 2,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 5,64</t>
+          <t>-3,49; 6,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 8,72</t>
+          <t>-0,19; 8,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,85; -2,45</t>
+          <t>-8,82; -1,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,09; 25,12</t>
+          <t>-46,43; 25,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 54,38</t>
+          <t>-22,19; 54,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 107,36</t>
+          <t>-3,83; 103,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-47,35; -14,27</t>
+          <t>-43,55; -10,04</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28,78</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>172,3%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 3,78</t>
+          <t>-5,59; 3,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 3,97</t>
+          <t>-8,54; 3,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 7,35</t>
+          <t>-2,26; 7,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 61,62</t>
+          <t>-2,81; 5,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 41,68</t>
+          <t>-40,07; 44,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,98; 30,94</t>
+          <t>-44,73; 31,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 100,19</t>
+          <t>-19,02; 100,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 416,86</t>
+          <t>-14,7; 35,27</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,02</t>
+          <t>7,59</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 7,81</t>
+          <t>-4,95; 7,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 9,11</t>
+          <t>-5,17; 9,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,42; 14,33</t>
+          <t>3,37; 14,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 12,58</t>
+          <t>1,97; 12,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-25,32; 65,39</t>
+          <t>-26,52; 66,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 55,64</t>
+          <t>-21,31; 59,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,56; 223,75</t>
+          <t>29,01; 234,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,62; 50,84</t>
+          <t>6,08; 51,55</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,15; 2,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,53</t>
+          <t>0,43; 3,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,02</t>
+          <t>0,46; 3,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 21,7</t>
+          <t>-0,6; 2,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 44,34</t>
+          <t>1,9; 45,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,91; 40,93</t>
+          <t>4,09; 41,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,5; 47,37</t>
+          <t>6,53; 48,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,94; 181,22</t>
+          <t>-4,1; 18,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_lim_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_lim_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
